--- a/Hoàng/2025/T4/CÔNG TY TNHH TK ELEVATOR VIỆT NAM (55-2025)/DS, DM - CÔNG TY TNHH TK ELEVATOR VIỆT NAM.xlsx
+++ b/Hoàng/2025/T4/CÔNG TY TNHH TK ELEVATOR VIỆT NAM (55-2025)/DS, DM - CÔNG TY TNHH TK ELEVATOR VIỆT NAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA-TN\Hoàng\2025\CÔNG TY TNHH TK ELEVATOR VIỆT NAM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T4\CÔNG TY TNHH TK ELEVATOR VIỆT NAM (55-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59164E7-D038-4511-8836-9C4F0DE8690B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6AB77A-8010-4967-AD51-E6DB32122758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS" sheetId="1" r:id="rId1"/>
@@ -272,25 +272,25 @@
     <t>MÃ NV</t>
   </si>
   <si>
-    <t>NV01</t>
-  </si>
-  <si>
-    <t>NV02</t>
-  </si>
-  <si>
-    <t>NV03</t>
-  </si>
-  <si>
-    <t>NV04</t>
-  </si>
-  <si>
-    <t>NV05</t>
-  </si>
-  <si>
-    <t>NV06</t>
-  </si>
-  <si>
-    <t>NV07</t>
+    <t>TK01</t>
+  </si>
+  <si>
+    <t>TK05</t>
+  </si>
+  <si>
+    <t>TK07</t>
+  </si>
+  <si>
+    <t>TK08</t>
+  </si>
+  <si>
+    <t>TK06</t>
+  </si>
+  <si>
+    <t>TK03</t>
+  </si>
+  <si>
+    <t>TK09</t>
   </si>
 </sst>
 </file>
@@ -301,7 +301,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -366,7 +366,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -898,16 +898,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -924,7 +924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -941,7 +941,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -958,7 +958,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -975,7 +975,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -992,7 +992,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1053,14 +1053,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEF5FA8-E8AA-4AA0-A755-E098B655B41C}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="36"/>
       <c r="B3" s="38"/>
       <c r="C3" s="40"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E3" s="36"/>
     </row>
-    <row r="4" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36"/>
       <c r="B4" s="38"/>
       <c r="C4" s="40"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="E4" s="36"/>
     </row>
-    <row r="5" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
       <c r="B5" s="38"/>
       <c r="C5" s="40"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E5" s="36"/>
     </row>
-    <row r="6" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="38"/>
       <c r="C6" s="40"/>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E6" s="36"/>
     </row>
-    <row r="7" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37"/>
       <c r="B7" s="27"/>
       <c r="C7" s="41"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E7" s="37"/>
     </row>
-    <row r="8" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>3</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>4</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>5</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="91.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="90" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>6</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="78.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="90" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>7</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>8</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>9</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>10</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>11</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>12</v>
       </c>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E18" s="29"/>
     </row>
-    <row r="19" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>13</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>14</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>15</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>16</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>17</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>18</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>19</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>20</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="39.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>21</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>22</v>
       </c>
